--- a/Technical_and_Functional_Compliance_Matrix_Bank_Asia_LMS.xlsx
+++ b/Technical_and_Functional_Compliance_Matrix_Bank_Asia_LMS.xlsx
@@ -58,12 +58,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t/>
+          <t>Skoder LMS Enterprise is engineered on a modern N-tier, modular microservices-ready architecture using high-performance PHP/Laravel framework and PostgreSQL/Oracle enterprise database. Comprehensive system documentation, API gateway specs, HA/DR failover topology, and data flow diagrams are included in the Technical Proposal.</t>
         </is>
       </c>
     </row>
@@ -80,7 +80,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied - Fully complied. Sized for Bank Asia's on-premises enterprise DC &amp; DR deployment utilizing Dell PowerEdge R760 Rack Servers, VMware vSphere 8, and RHEL 9. Detailed server BoQ and architecture attached in Table 16 and separate Hardware Quotation.</t>
         </is>
       </c>
     </row>
@@ -104,12 +104,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Skoder Technologies operates a dedicated Level 1/2/3 technical helpdesk from 09:00 AM to 08:00 PM Sunday through Thursday, with 24/7/365 emergency on-call and remote incident resolution via ticketing portal, email, and phone.</t>
         </is>
       </c>
     </row>
@@ -126,12 +126,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. The platform includes an advanced dynamic query builder allowing custom search filters across case types, borrower TIN/NID, court stages, outstanding balances, and hearing dates with export to Excel/PDF.</t>
         </is>
       </c>
     </row>
@@ -148,12 +148,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Includes comprehensive web-based management console, Prometheus/Grafana health metrics endpoints, APM monitoring, and secure SSL VPN administrative access.</t>
         </is>
       </c>
     </row>
@@ -170,12 +170,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. 100% browser-independent responsive web interface built on HTML5, CSS3, and modern JavaScript, fully supported on latest Google Chrome, Microsoft Edge, Mozilla Firefox, and Apple Safari without plugins.</t>
         </is>
       </c>
     </row>
@@ -192,12 +192,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Supports bilingual English and Bengali (Unicode UTF-8 / Nikosh / SolaimanLipi) for legal notices, court cause lists, case summaries, and statutory reports.</t>
         </is>
       </c>
     </row>
@@ -214,12 +214,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated test execution framework supported using simulated API payloads and automated regression test scripts for UAT verification.</t>
         </is>
       </c>
     </row>
@@ -236,12 +236,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Perpetual enterprise bank-wide license covers Primary Data Center (DC), Near DR, and Far DR active-passive deployment without additional per-core or per-seat licensing penalties.</t>
         </is>
       </c>
     </row>
@@ -258,12 +258,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic Master Parameter Setup module allows authorized administrators to configure court codes, case classifications, expense heads, branch codes, and legal acts.</t>
         </is>
       </c>
     </row>
@@ -280,12 +280,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Bank Asia PLC branding, official logo, and branch headers are dynamically rendered across application headers, printable legal notices, Jari statements, and reports.</t>
         </is>
       </c>
     </row>
@@ -302,12 +302,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive administrative console provided for schema configurations, workflow rules, audit log review, role management, and routine operational maintenance.</t>
         </is>
       </c>
     </row>
@@ -324,12 +324,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Enforces TLS 1.3 / HTTPS encryption across all web interfaces and API endpoints with strong cipher suites (HSTS, forward secrecy).</t>
         </is>
       </c>
     </row>
@@ -346,12 +346,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Modular architecture allows rapid local customization of validation rules, form fields, court stages, and screen layouts based on Bank Asia's specific legal workflows.</t>
         </is>
       </c>
     </row>
@@ -368,12 +368,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Designed to operate within Bank Asia's secure internal network zone / dedicated DMZ/VLAN with mutual TLS (mTLS) and IP whitelisting for CBS integration.</t>
         </is>
       </c>
     </row>
@@ -390,12 +390,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Supports automated End-of-Day (EOD) cron scheduling, ETL batch synchronisation, and real-time delta fetching for classified loan balances and customer details.</t>
         </is>
       </c>
     </row>
@@ -412,12 +412,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Features robust RESTful and SOAP API gateways with JSON/XML payloads, JWT token authentication, and rate limiting for bidirectional CBS/peripheral system integration.</t>
         </is>
       </c>
     </row>
@@ -434,12 +434,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Strong AES-256 column-level encryption for confidential PII and financial records at rest; TLS 1.3 encryption for all data in transit across networks.</t>
         </is>
       </c>
     </row>
@@ -463,12 +463,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Built upon open, standard architectural patterns (REST APIs, microservices, OpenAPI/Swagger 3.0 specs) ensuring seamless integration with Bank Asia CBS and other banking modules.</t>
         </is>
       </c>
     </row>
@@ -485,12 +485,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Native support for enterprise Single Sign-On (SSO) via Active Directory (LDAP / Kerberos / SAML 2.0 / OAuth2 / OpenID Connect) and open banking API integration.</t>
         </is>
       </c>
     </row>
@@ -507,12 +507,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Extensible modular schema design supports dynamic custom attributes and backwards-compatible API versioning to absorb CBS upgrades without downtime.</t>
         </is>
       </c>
     </row>
@@ -529,12 +529,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Native integration with Bank Asia's internal SMS Gateway (SMPP / HTTP REST) and enterprise SMTP / Microsoft Exchange email servers for automated alert delivery.</t>
         </is>
       </c>
     </row>
@@ -551,12 +551,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Notification engine handles both SMS and email queues with failure retry mechanisms and delivery audit logging.</t>
         </is>
       </c>
     </row>
@@ -573,12 +573,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated background scheduler dispatches upcoming court hearing reminders, legal notice deadlines, and warrant execution alerts via SMS and email on configurable intervals.</t>
         </is>
       </c>
     </row>
@@ -595,12 +595,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Provides read-replica database support and automated daily ETL pipelines / data staging views for Bank Asia's Central Data Warehouse / MIS reporting.</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive integration toolkit including REST/JSON, SOAP/XML, automated SFTP batch file exchange, and OpenAPI/Swagger documentation.</t>
         </is>
       </c>
     </row>
@@ -646,12 +646,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Case document repository maintains immutable version control, timestamped revision history, and one-click rollback/retrieval of historical file versions.</t>
         </is>
       </c>
     </row>
@@ -668,12 +668,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated real-time notifications dispatched to assigned case handlers, desk officials, and legal supervisors whenever case status or documents are modified.</t>
         </is>
       </c>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive data migration strategy, automated Excel/CSV ETL ingest utilities, data cleansing scripts, and validation audits ensure 100% legacy litigation data migration.</t>
         </is>
       </c>
     </row>
@@ -712,12 +712,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Pre-migration gap analysis, automated staging tables with validation rules, and manual reconciliation workflows handle unmapped or missing legacy attributes.</t>
         </is>
       </c>
     </row>
@@ -741,12 +741,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Flexible workflow engine allows concurrent parallel tracking of civil suits (Artha Rin), criminal proceedings (NI Act 138), auction notices, and writ petitions for the same borrower.</t>
         </is>
       </c>
     </row>
@@ -770,12 +770,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Parameterized business rules engine supports configurable escalation rules, mandatory legal notice statutory wait periods (e.g. 30 days under NI Act), and approval limits.</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Multi-tier permission matrix enforces granular restrictions per user role, branch, and division for drafting, maker approval, checker authorization, viewing, and exporting reports.</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Detailed enterprise deployment architecture diagram depicting Web Server, App Server, DB Cluster, CBS Gateway, SMS/Email Server, and Active Directory enclosed in Technical Proposal.</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Proposed 100% on-premises deployment adhering to Bangladesh Bank ICT Guidelines for full data sovereignty across Bank Asia Primary DC and DR sites.</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Three distinct, isolated environments (Development/Test, UAT/Staging, and Production) will be provisioned, configured, and maintained during rollout.</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. 100% perpetual bank-wide enterprise license with unlimited users, branches, and cases without recurring subscription or license expiry locks.</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Granular RBAC supporting administrative, legal officer, branch maker, branch checker, panel lawyer, and executive management roles with immutable audit logging.</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Passwords hashed using industry-standard bcrypt / Argon2id algorithms with cryptographic salt, ensuring zero plain-text storage.</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Database stores one-way salted cryptographic hashes adhering to Bangladesh Bank Information Security Standards.</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Configurable password complexity policy (minimum length, uppercase, lowercase, numbers, special characters, expiration intervals, password history prevention).</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Seamless Single Sign-On (SSO) supported via Active Directory LDAP / SAML 2.0 / Kerberos integration.</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Supports assigning multiple complementary roles to a single user profile while preserving strict Maker-Checker segregation of duties.</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. System administrators can reassign user roles, transfer branch assignments, and adjust approval limits instantly with full audit logging.</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Strict Maker-Checker access matrix defined and administered through graphical administrative interface.</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Menu items, form actions (Create, Edit, Delete, Authorize), and data access scopes are dynamically restricted per assigned role.</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Fully integrated with Microsoft Active Directory / Azure AD via secure LDAP/LDAPS for centralized authentication and automated user provisioning.</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable audit trail captures user ID, client IP, timestamp, action type, old values, and new values for every create, update, delete, and view event.</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Database-level AES-256 transparent data encryption (TDE) for data at rest and TLS 1.3 encryption for data in transit across all endpoints.</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Supports hierarchical user group definitions (Legal Division, Special Asset Management, Branch Recovery, Panel Lawyers, Executive Management).</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Parameterized security rules enforce IP whitelisting per user/branch, allowed operating business hours, and authorized application server bindings.</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Self-service password reset workflow with secure one-time password (OTP) verification sent to registered official mobile and email.</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Configurable idle session timeout (default 15 minutes) automatically terminates inactive sessions and clears client-side tokens.</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Administrators can immediately lock, deactivate, or reactivate user accounts with mandatory reason logging and audit trail recording.</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Concurrent login prevention enforces single active session per user ID; subsequent logins invalidate existing sessions or are blocked.</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Advanced ad-hoc reporting module allows authorized users to construct parameterized queries, filter audit trails, and export datasets to Excel/PDF.</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Account automatically locks after parameterized number of consecutive failed attempts (default 5 attempts), requiring admin unlock or OTP verification.</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Active-passive high-availability configuration supported with automated database replication to Bank Asia DR site and documented BCP/DR runbook.</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Engineered for 99.9% uptime with automated health checks, seamless DR failover procedures, RPO &lt; 5 minutes, and RTO &lt; 15 minutes.</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. ACID-compliant transactional database engine with Write-Ahead Logging (WAL) ensures complete data integrity and automated crash recovery upon restart.</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Fault-tolerant services with state recovery mechanisms ensure zero transaction loss and immediate resumption of operations upon system reboot.</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated error tracking and anomaly detection engine alerts system administrators via email and dashboard notifications upon application exceptions.</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive enterprise RBAC model strictly enforces segregation of duties between Maker, Checker, Approver, and Viewer roles.</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Pre-built connector for Microsoft Active Directory / LDAPS provides single-source credential verification and role mapping.</t>
         </is>
       </c>
     </row>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Passwords stored using salted SHA-256 / bcrypt cryptographic hashing; no plain-text passwords stored under any circumstances.</t>
         </is>
       </c>
     </row>
@@ -1583,12 +1583,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. 100% browser-independent web client compatible with Windows, macOS, and Linux on Chrome, Edge, Firefox, and Safari; backend compatible with RHEL and PostgreSQL/Oracle.</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Hardened application security layer featuring rate limiting, CSRF tokens, XSS sanitization, parameterized SQL queries, and secure session headers.</t>
         </is>
       </c>
     </row>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Built and audited according to OWASP Top 10 security standards; certified against SQL Injection, XSS, CSRF, broken access control, and insecure deserialization.</t>
         </is>
       </c>
     </row>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated batch execution log monitors CBS daily data ingestion, records record-level success/error counts, failure reasons, and issues alert notifications.</t>
         </is>
       </c>
     </row>
@@ -1671,12 +1671,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Global exception handling intercepts all errors, logging detailed stack traces internally while presenting secure, user-friendly messages to the end user.</t>
         </is>
       </c>
     </row>
@@ -1693,12 +1693,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Enforces TLS 1.3 / HTTPS encryption across all client-server interactions and inter-service communications with HSTS headers.</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Audit log search console allows authorized security officers to filter logs by user ID, action type, date range, IP address, and module.</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Built on open standards (REST, container-ready, standard SQL, POSIX OS) ensuring forward compatibility with upcoming hardware, OS, and DB upgrades.</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Skoder Technologies provides rapid vulnerability remediation and hotfix patch releases within 24–48 hours upon issuance of critical security advisories.</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Supports device fingerprinting, client certificate validation, and MAC/IP binding to restrict application access to authorized corporate terminals.</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Skoder Technologies provides comprehensive Infrastructure &amp; Application Security Hardening Guidelines covering OS, DB, Web Server, and network policies.</t>
         </is>
       </c>
     </row>
@@ -1825,12 +1825,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Compatible with enterprise SIEM solutions (Splunk, IBM QRadar, ELK), Web Application Firewalls (WAF), and endpoint protection systems.</t>
         </is>
       </c>
     </row>
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. 100% of underlying frameworks, libraries, and runtime dependencies are licensed under permissive enterprise open-source licenses, fully updated and free from known CVE vulnerabilities.</t>
         </is>
       </c>
     </row>
@@ -1915,12 +1915,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive User Group Management core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full-lifecycle enterprise user access management with granular permissions and audit logging.</t>
         </is>
       </c>
     </row>
@@ -1959,12 +1959,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Granular user group management with dynamic access rights and role-based privilege mapping.</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Granular user group management with dynamic access rights and role-based privilege mapping.</t>
         </is>
       </c>
     </row>
@@ -2003,12 +2003,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Granular user group management with dynamic access rights and role-based privilege mapping.</t>
         </is>
       </c>
     </row>
@@ -2025,12 +2025,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Granular user group management with dynamic access rights and role-based privilege mapping.</t>
         </is>
       </c>
     </row>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Granular user group management with dynamic access rights and role-based privilege mapping.</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Granular user group management with dynamic access rights and role-based privilege mapping.</t>
         </is>
       </c>
     </row>
@@ -2091,12 +2091,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive User Management core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -2113,12 +2113,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full-lifecycle enterprise user access management with granular permissions and audit logging.</t>
         </is>
       </c>
     </row>
@@ -2135,12 +2135,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Granular user group management with dynamic access rights and role-based privilege mapping.</t>
         </is>
       </c>
     </row>
@@ -2157,12 +2157,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full-lifecycle enterprise user access management with granular permissions and audit logging.</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2179,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full-lifecycle enterprise user access management with granular permissions and audit logging.</t>
         </is>
       </c>
     </row>
@@ -2201,12 +2201,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full-lifecycle enterprise user access management with granular permissions and audit logging.</t>
         </is>
       </c>
     </row>
@@ -2223,12 +2223,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Built-in Maker-Checker workflow for user account provisioning and access privilege authorization.</t>
         </is>
       </c>
     </row>
@@ -2245,12 +2245,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Built-in Maker-Checker workflow for user account provisioning and access privilege authorization.</t>
         </is>
       </c>
     </row>
@@ -2267,12 +2267,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -2289,12 +2289,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full-lifecycle enterprise user access management with granular permissions and audit logging.</t>
         </is>
       </c>
     </row>
@@ -2311,12 +2311,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full-lifecycle enterprise user access management with granular permissions and audit logging.</t>
         </is>
       </c>
     </row>
@@ -2333,12 +2333,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full-lifecycle enterprise user access management with granular permissions and audit logging.</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Configurable session timeout policy enforced server-side with automatic session termination.</t>
         </is>
       </c>
     </row>
@@ -2377,12 +2377,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Hardened password security policy with encrypted salted storage, lockout policy, and self-service reset.</t>
         </is>
       </c>
     </row>
@@ -2399,12 +2399,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Login core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -2421,12 +2421,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Hardened password security policy with encrypted salted storage, lockout policy, and self-service reset.</t>
         </is>
       </c>
     </row>
@@ -2443,12 +2443,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Hardened password security policy with encrypted salted storage, lockout policy, and self-service reset.</t>
         </is>
       </c>
     </row>
@@ -2465,12 +2465,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Hardened password security policy with encrypted salted storage, lockout policy, and self-service reset.</t>
         </is>
       </c>
     </row>
@@ -2487,12 +2487,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Parameter Management core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -2509,12 +2509,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Department with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2531,12 +2531,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Designation with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Functional Designation with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2575,12 +2575,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Case Type with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2597,12 +2597,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Security Status/Details with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2619,12 +2619,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Auction Status with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2641,12 +2641,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Business Status/ Nature with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Borrower Status with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Guarantor Status with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Loan/investment Segment nature with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2729,12 +2729,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Cheque Status with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2751,12 +2751,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Facility/investment Type with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2773,12 +2773,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Case Steps with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Retail Branch with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2817,12 +2817,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for District with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2839,12 +2839,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Branch with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Expense Type with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2883,12 +2883,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Court Type with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2905,12 +2905,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Court List with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2927,12 +2927,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Lawyer List with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2949,12 +2949,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Functional Designation with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2971,12 +2971,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Disposal Status with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Paper List with add option with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3015,12 +3015,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Paper Vendor List with add option with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3037,12 +3037,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for CL Status with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Nature Of Warrant of Arrest and status of W/A with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3081,12 +3081,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Expense activities with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3103,12 +3103,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Supreme Court (SC) Case Category with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Supreme Court (SC) Case Type with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3147,12 +3147,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Supreme Court (SC) Case Status with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3169,12 +3169,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Execution Criteria /Stage of Execution Case with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3191,12 +3191,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for Appeal Bail Type with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3213,12 +3213,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for schedule charges case against bank with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for schedule charges legal affairs (Litigation/ Documentation/Others with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3257,12 +3257,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for related authority with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3279,12 +3279,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic master parameter configuration for HC Division and AD with Maker-Checker validation and audit history.</t>
         </is>
       </c>
     </row>
@@ -3301,12 +3301,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic court holiday calendar configuration with distinction between Supreme Court and subordinate courts.</t>
         </is>
       </c>
     </row>
@@ -3323,12 +3323,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic court holiday calendar configuration with distinction between Supreme Court and subordinate courts.</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic court holiday calendar configuration with distinction between Supreme Court and subordinate courts.</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic court holiday calendar configuration with distinction between Supreme Court and subordinate courts.</t>
         </is>
       </c>
     </row>
@@ -3389,12 +3389,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dynamic court holiday calendar configuration with distinction between Supreme Court and subordinate courts.</t>
         </is>
       </c>
     </row>
@@ -3411,12 +3411,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Lawyer Package Bill Setup core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -3433,12 +3433,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive lawyer billing package configuration supporting stage-wise tariffs, fee extensions, and approval workflows.</t>
         </is>
       </c>
     </row>
@@ -3455,12 +3455,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive lawyer billing package configuration supporting stage-wise tariffs, fee extensions, and approval workflows.</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive lawyer billing package configuration supporting stage-wise tariffs, fee extensions, and approval workflows.</t>
         </is>
       </c>
     </row>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive lawyer billing package configuration supporting stage-wise tariffs, fee extensions, and approval workflows.</t>
         </is>
       </c>
     </row>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive lawyer billing package configuration supporting stage-wise tariffs, fee extensions, and approval workflows.</t>
         </is>
       </c>
     </row>
@@ -3543,12 +3543,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive lawyer billing package configuration supporting stage-wise tariffs, fee extensions, and approval workflows.</t>
         </is>
       </c>
     </row>
@@ -3565,12 +3565,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive lawyer billing package configuration supporting stage-wise tariffs, fee extensions, and approval workflows.</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Dashboard core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -3609,12 +3609,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time executive dashboard featuring daily court cause lists, hearing calendars, notice statuses, and recovery metrics.</t>
         </is>
       </c>
     </row>
@@ -3631,12 +3631,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive 1st Legal Notice/ Reminder Notice core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -3653,12 +3653,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated bilingual legal notice generator with CBS borrower data integration, serving history, and Maker-Checker approval.</t>
         </is>
       </c>
     </row>
@@ -3675,12 +3675,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated bilingual legal notice generator with CBS borrower data integration, serving history, and Maker-Checker approval.</t>
         </is>
       </c>
     </row>
@@ -3697,12 +3697,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated bilingual legal notice generator with CBS borrower data integration, serving history, and Maker-Checker approval.</t>
         </is>
       </c>
     </row>
@@ -3719,12 +3719,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated bilingual legal notice generator with CBS borrower data integration, serving history, and Maker-Checker approval.</t>
         </is>
       </c>
     </row>
@@ -3741,12 +3741,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated bilingual legal notice generator with CBS borrower data integration, serving history, and Maker-Checker approval.</t>
         </is>
       </c>
     </row>
@@ -3763,12 +3763,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated bilingual legal notice generator with CBS borrower data integration, serving history, and Maker-Checker approval.</t>
         </is>
       </c>
     </row>
@@ -3785,12 +3785,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated bilingual legal notice generator with CBS borrower data integration, serving history, and Maker-Checker approval.</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3807,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated bilingual legal notice generator with CBS borrower data integration, serving history, and Maker-Checker approval.</t>
         </is>
       </c>
     </row>
@@ -3829,12 +3829,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Case Merit Analysis (CMA) core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -3851,12 +3851,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
         </is>
       </c>
     </row>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
         </is>
       </c>
     </row>
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
         </is>
       </c>
     </row>
@@ -3961,12 +3961,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
         </is>
       </c>
     </row>
@@ -3983,12 +3983,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
         </is>
       </c>
     </row>
@@ -4005,12 +4005,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -4027,12 +4027,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
         </is>
       </c>
     </row>
@@ -4049,12 +4049,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -4071,12 +4071,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
         </is>
       </c>
     </row>
@@ -4093,12 +4093,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -4115,12 +4115,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -4137,12 +4137,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4181,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
         </is>
       </c>
     </row>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -4225,12 +4225,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
         </is>
       </c>
     </row>
@@ -4291,12 +4291,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Auction Management core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -4313,12 +4313,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Legally compliant Artha Rin Adalat Section 12(3), 33(5), 33(7) auction workflow, newspaper notice publishing, and bidder register.</t>
         </is>
       </c>
     </row>
@@ -4335,12 +4335,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Legally compliant Artha Rin Adalat Section 12(3), 33(5), 33(7) auction workflow, newspaper notice publishing, and bidder register.</t>
         </is>
       </c>
     </row>
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Legally compliant Artha Rin Adalat Section 12(3), 33(5), 33(7) auction workflow, newspaper notice publishing, and bidder register.</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Legally compliant Artha Rin Adalat Section 12(3), 33(5), 33(7) auction workflow, newspaper notice publishing, and bidder register.</t>
         </is>
       </c>
     </row>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Legally compliant Artha Rin Adalat Section 12(3), 33(5), 33(7) auction workflow, newspaper notice publishing, and bidder register.</t>
         </is>
       </c>
     </row>
@@ -4423,12 +4423,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Legally compliant Artha Rin Adalat Section 12(3), 33(5), 33(7) auction workflow, newspaper notice publishing, and bidder register.</t>
         </is>
       </c>
     </row>
@@ -4445,12 +4445,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Legally compliant Artha Rin Adalat Section 12(3), 33(5), 33(7) auction workflow, newspaper notice publishing, and bidder register.</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -4489,12 +4489,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -4533,12 +4533,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -4555,12 +4555,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -4577,12 +4577,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -4621,12 +4621,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
         </is>
       </c>
     </row>
@@ -4643,12 +4643,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -4687,12 +4687,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Account Statement Generation core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated CBS account statement and execution suit (Jari) certificate generation under Bankers' Books Evidence Act.</t>
         </is>
       </c>
     </row>
@@ -4731,12 +4731,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Bi-directional CBS integration via secure REST API gateway for real-time account data and ledger sync.</t>
         </is>
       </c>
     </row>
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated CBS account statement and execution suit (Jari) certificate generation under Bankers' Books Evidence Act.</t>
         </is>
       </c>
     </row>
@@ -4775,12 +4775,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated CBS account statement and execution suit (Jari) certificate generation under Bankers' Books Evidence Act.</t>
         </is>
       </c>
     </row>
@@ -4797,12 +4797,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Jari Statement with Certificate core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -4819,12 +4819,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated CBS account statement and execution suit (Jari) certificate generation under Bankers' Books Evidence Act.</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated CBS account statement and execution suit (Jari) certificate generation under Bankers' Books Evidence Act.</t>
         </is>
       </c>
     </row>
@@ -4863,12 +4863,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated CBS account statement and execution suit (Jari) certificate generation under Bankers' Books Evidence Act.</t>
         </is>
       </c>
     </row>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Lower Court Suit Management core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -4907,12 +4907,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
         </is>
       </c>
     </row>
@@ -4929,12 +4929,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
         </is>
       </c>
     </row>
@@ -4951,12 +4951,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
         </is>
       </c>
     </row>
@@ -4973,12 +4973,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -4995,12 +4995,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
         </is>
       </c>
     </row>
@@ -5017,12 +5017,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -5039,12 +5039,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -5105,12 +5105,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -5127,12 +5127,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -5149,12 +5149,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
         </is>
       </c>
     </row>
@@ -5171,12 +5171,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -5193,12 +5193,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -5215,12 +5215,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
         </is>
       </c>
     </row>
@@ -5237,12 +5237,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Case Steps update core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -5259,12 +5259,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
         </is>
       </c>
     </row>
@@ -5303,12 +5303,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
         </is>
       </c>
     </row>
@@ -5325,12 +5325,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
         </is>
       </c>
     </row>
@@ -5347,12 +5347,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -5369,12 +5369,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
         </is>
       </c>
     </row>
@@ -5413,12 +5413,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -5435,12 +5435,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -5457,12 +5457,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -5479,12 +5479,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -5501,12 +5501,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
         </is>
       </c>
     </row>
@@ -5523,12 +5523,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -5567,12 +5567,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
         </is>
       </c>
     </row>
@@ -5589,12 +5589,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Arising Case from Original Case core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -5611,12 +5611,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Hierarchical linking of arising cases (Execution suits, Session cases, Appeals) with integrated case history mapping.</t>
         </is>
       </c>
     </row>
@@ -5633,12 +5633,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Hierarchical linking of arising cases (Execution suits, Session cases, Appeals) with integrated case history mapping.</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Hierarchical linking of arising cases (Execution suits, Session cases, Appeals) with integrated case history mapping.</t>
         </is>
       </c>
     </row>
@@ -5677,12 +5677,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Hierarchical linking of arising cases (Execution suits, Session cases, Appeals) with integrated case history mapping.</t>
         </is>
       </c>
     </row>
@@ -5699,12 +5699,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Hierarchical linking of arising cases (Execution suits, Session cases, Appeals) with integrated case history mapping.</t>
         </is>
       </c>
     </row>
@@ -5721,12 +5721,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -5765,12 +5765,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
         </is>
       </c>
     </row>
@@ -5787,12 +5787,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -5831,12 +5831,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
         </is>
       </c>
     </row>
@@ -5875,12 +5875,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -5897,12 +5897,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -5919,12 +5919,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Bill Processing and Disbursement Module core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -5941,12 +5941,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
         </is>
       </c>
     </row>
@@ -6007,12 +6007,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
         </is>
       </c>
     </row>
@@ -6029,12 +6029,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
         </is>
       </c>
     </row>
@@ -6051,12 +6051,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -6117,12 +6117,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -6139,12 +6139,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -6161,12 +6161,12 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Bi-directional CBS integration via secure REST API gateway for real-time account data and ledger sync.</t>
         </is>
       </c>
     </row>
@@ -6183,12 +6183,12 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
         </is>
       </c>
     </row>
@@ -6205,12 +6205,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -6249,12 +6249,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated dynamic PDF generation with official Bank Asia branding and digital/physical signature blocks.</t>
         </is>
       </c>
     </row>
@@ -6271,12 +6271,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -6337,12 +6337,12 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
         </is>
       </c>
     </row>
@@ -6359,12 +6359,12 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -6381,12 +6381,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -6403,12 +6403,12 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Court Fee Return and Adjustment core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -6447,12 +6447,12 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Transparent management and ledger tracking of unutilized court fees with return and future-case adjustment facilities.</t>
         </is>
       </c>
     </row>
@@ -6469,12 +6469,12 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Transparent management and ledger tracking of unutilized court fees with return and future-case adjustment facilities.</t>
         </is>
       </c>
     </row>
@@ -6491,12 +6491,12 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Transparent management and ledger tracking of unutilized court fees with return and future-case adjustment facilities.</t>
         </is>
       </c>
     </row>
@@ -6513,12 +6513,12 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Transparent management and ledger tracking of unutilized court fees with return and future-case adjustment facilities.</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -6557,12 +6557,12 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -6579,12 +6579,12 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -6601,12 +6601,12 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Bi-directional CBS integration via secure REST API gateway for real-time account data and ledger sync.</t>
         </is>
       </c>
     </row>
@@ -6623,12 +6623,12 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -6711,12 +6711,12 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -6733,12 +6733,12 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -6777,12 +6777,12 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive HC &amp; AD Matters Feature core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -6821,12 +6821,12 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated Supreme Court (High Court Division &amp; Appellate Division) suit management with case linking and order archiving.</t>
         </is>
       </c>
     </row>
@@ -6843,12 +6843,12 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -6865,12 +6865,12 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated Supreme Court (High Court Division &amp; Appellate Division) suit management with case linking and order archiving.</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated Supreme Court (High Court Division &amp; Appellate Division) suit management with case linking and order archiving.</t>
         </is>
       </c>
     </row>
@@ -6909,12 +6909,12 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated Supreme Court (High Court Division &amp; Appellate Division) suit management with case linking and order archiving.</t>
         </is>
       </c>
     </row>
@@ -6931,12 +6931,12 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -6953,12 +6953,12 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -6975,12 +6975,12 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -7019,12 +7019,12 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -7041,12 +7041,12 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -7063,12 +7063,12 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
         </is>
       </c>
     </row>
@@ -7085,12 +7085,12 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -7107,12 +7107,12 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -7129,12 +7129,12 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
         </is>
       </c>
     </row>
@@ -7151,12 +7151,12 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
         </is>
       </c>
     </row>
@@ -7173,12 +7173,12 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
         </is>
       </c>
     </row>
@@ -7195,12 +7195,12 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
         </is>
       </c>
     </row>
@@ -7239,12 +7239,12 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -7261,12 +7261,12 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -7283,12 +7283,12 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
         </is>
       </c>
     </row>
@@ -7305,12 +7305,12 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -7349,12 +7349,12 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
         </is>
       </c>
     </row>
@@ -7393,12 +7393,12 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -7415,12 +7415,12 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -7437,12 +7437,12 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
         </is>
       </c>
     </row>
@@ -7459,12 +7459,12 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
         </is>
       </c>
     </row>
@@ -7481,12 +7481,12 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
         </is>
       </c>
     </row>
@@ -7503,12 +7503,12 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
         </is>
       </c>
     </row>
@@ -7525,12 +7525,12 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
         </is>
       </c>
     </row>
@@ -7547,12 +7547,12 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -7591,12 +7591,12 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -7613,12 +7613,12 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
         </is>
       </c>
     </row>
@@ -7635,12 +7635,12 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -7657,12 +7657,12 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -7679,12 +7679,12 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -7701,12 +7701,12 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -7723,12 +7723,12 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -7745,12 +7745,12 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Authorization Management core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -7767,12 +7767,12 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Branch-to-HO authorization workflow for plaintiff changes, case withdrawals, bail money, and court transfers.</t>
         </is>
       </c>
     </row>
@@ -7789,12 +7789,12 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Branch-to-HO authorization workflow for plaintiff changes, case withdrawals, bail money, and court transfers.</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Branch-to-HO authorization workflow for plaintiff changes, case withdrawals, bail money, and court transfers.</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Branch-to-HO authorization workflow for plaintiff changes, case withdrawals, bail money, and court transfers.</t>
         </is>
       </c>
     </row>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Branch-to-HO authorization workflow for plaintiff changes, case withdrawals, bail money, and court transfers.</t>
         </is>
       </c>
     </row>
@@ -7877,12 +7877,12 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Branch-to-HO authorization workflow for plaintiff changes, case withdrawals, bail money, and court transfers.</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -7943,12 +7943,12 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
         </is>
       </c>
     </row>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -7987,12 +7987,12 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated dynamic PDF generation with official Bank Asia branding and digital/physical signature blocks.</t>
         </is>
       </c>
     </row>
@@ -8009,12 +8009,12 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -8031,12 +8031,12 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -8053,12 +8053,12 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
         </is>
       </c>
     </row>
@@ -8075,12 +8075,12 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -8097,12 +8097,12 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -8119,12 +8119,12 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Warrant Of Arrest Management core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -8141,12 +8141,12 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end Warrant of Arrest (WOA) tracking, arrest history register, police station execution logs, and expense accounting.</t>
         </is>
       </c>
     </row>
@@ -8163,12 +8163,12 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end Warrant of Arrest (WOA) tracking, arrest history register, police station execution logs, and expense accounting.</t>
         </is>
       </c>
     </row>
@@ -8185,12 +8185,12 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -8207,12 +8207,12 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -8229,12 +8229,12 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
         </is>
       </c>
     </row>
@@ -8273,12 +8273,12 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -8317,12 +8317,12 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -8339,12 +8339,12 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -8361,12 +8361,12 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -8383,12 +8383,12 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. End-to-end Warrant of Arrest (WOA) tracking, arrest history register, police station execution logs, and expense accounting.</t>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Appeal Bail Money Deposit &amp; Withdraw Management core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Responsive web portal and secure mobile-optimized interface with MFA authentication for on-the-go legal officers.</t>
         </is>
       </c>
     </row>
@@ -8449,12 +8449,12 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -8471,12 +8471,12 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -8493,12 +8493,12 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Statutory appeal bail pre-deposit register, challan receipt archiving, withdrawal reconciliation, and audit trail.</t>
         </is>
       </c>
     </row>
@@ -8515,12 +8515,12 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -8537,12 +8537,12 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -8559,12 +8559,12 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -8603,12 +8603,12 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
         </is>
       </c>
     </row>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
         </is>
       </c>
     </row>
@@ -8647,12 +8647,12 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
         </is>
       </c>
     </row>
@@ -8669,12 +8669,12 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -8691,12 +8691,12 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -8713,12 +8713,12 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Responsive web portal and secure mobile-optimized interface with MFA authentication for on-the-go legal officers.</t>
         </is>
       </c>
     </row>
@@ -8735,12 +8735,12 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Responsive web portal and secure mobile-optimized interface with MFA authentication for on-the-go legal officers.</t>
         </is>
       </c>
     </row>
@@ -8757,12 +8757,12 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Statutory appeal bail pre-deposit register, challan receipt archiving, withdrawal reconciliation, and audit trail.</t>
         </is>
       </c>
     </row>
@@ -8779,12 +8779,12 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Statutory appeal bail pre-deposit register, challan receipt archiving, withdrawal reconciliation, and audit trail.</t>
         </is>
       </c>
     </row>
@@ -8801,12 +8801,12 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Document Upload core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -8845,12 +8845,12 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -8867,12 +8867,12 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -8889,12 +8889,12 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -8911,12 +8911,12 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
         </is>
       </c>
     </row>
@@ -8977,12 +8977,12 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
         </is>
       </c>
     </row>
@@ -8999,12 +8999,12 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
         </is>
       </c>
     </row>
@@ -9021,12 +9021,12 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Reports core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -9043,12 +9043,12 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Fully compliant with Bangladesh Bank statutory reporting requirements (Reporting সংযোজনী- ক- for BB) with Excel/PDF export.</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Fully compliant with Bangladesh Bank statutory reporting requirements (Reporting সংযোজনী -খ for BB) with Excel/PDF export.</t>
         </is>
       </c>
     </row>
@@ -9087,12 +9087,12 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Fully compliant with Bangladesh Bank statutory reporting requirements (Reporting সংযোজনী-গ for BB) with Excel/PDF export.</t>
         </is>
       </c>
     </row>
@@ -9109,12 +9109,12 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Reporting. Total Case Summary/report for Management based on different nature of the case. with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9131,12 +9131,12 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Reporting/summery on cases by bank and against Bank in lower court/High Court. with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9153,12 +9153,12 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Fully compliant with Bangladesh Bank statutory reporting requirements (RIT and BR-4 for BB) with Excel/PDF export.</t>
         </is>
       </c>
     </row>
@@ -9175,12 +9175,12 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Fully compliant with Bangladesh Bank statutory reporting requirements (BB Audit-Artha Rin Suit) with Excel/PDF export.</t>
         </is>
       </c>
     </row>
@@ -9197,12 +9197,12 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for All Certificate Owned Property List [ (33(5) &amp; 33(7) separate certificate list] with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9219,12 +9219,12 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Fully compliant with Bangladesh Bank statutory reporting requirements (DBI 22 to BB) with Excel/PDF export.</t>
         </is>
       </c>
     </row>
@@ -9241,12 +9241,12 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for District wise Artha Rin case Statement/Court Wise Statement and other parameter with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Major Financial Indicator with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9285,12 +9285,12 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for CRMR with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9307,12 +9307,12 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for ISS Report with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9329,12 +9329,12 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Statement of Classified Loans &amp; Advances and Other Information with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9351,12 +9351,12 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Statement of Pending Cases/disposed cases/settled cases on different parameter required bank with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Taskforce Report with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9395,12 +9395,12 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Fully compliant with Bangladesh Bank statutory reporting requirements (Bangladesh Bank Case related details Statement) with Excel/PDF export.</t>
         </is>
       </c>
     </row>
@@ -9417,12 +9417,12 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Portfolio summery with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Segment wise summery with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9461,12 +9461,12 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Officer wise summery with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Case Disposal Summery with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Step Completion Report with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9527,12 +9527,12 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Lawyer Wise Summery with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for LRM wise Case Statement Step changed with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9571,12 +9571,12 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Case Pending at The Same Steps with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9593,12 +9593,12 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Time Duration between Last date &amp; Next Date with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9615,12 +9615,12 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Summary on Lawyer's Performance with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Court Location Wise Summary with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9659,12 +9659,12 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for HCD &amp; AD Pending Cases Statement (Summary) with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9681,12 +9681,12 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for HCD &amp; AD Case Filed Statement with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9703,12 +9703,12 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for HCD &amp; AD Portfolio Summery with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9725,12 +9725,12 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Pending Cases Statement (Lawyer/Law Firm wise/branch wise/month wise/quarter wise/half yearly wise/yearly) with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9747,12 +9747,12 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Disposed Cases Statement (Lawyer/Law Firm wise/branch wise/month wise/quarter wise/half yearly wise/yearly) with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9769,12 +9769,12 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for 1st Legal Notice served Report with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9791,12 +9791,12 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for CMA Report with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9813,12 +9813,12 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Lawyer Wise Legal Notice with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9835,12 +9835,12 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Summery On Recovery on different parameter (monthly/quarterly/half yearly/yearly and other parameter as required. with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9857,12 +9857,12 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Summery On Next Steps with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9879,12 +9879,12 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Summery on Closed Accounts with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9901,12 +9901,12 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Account Wise Lawyer Bill with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9923,12 +9923,12 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Lawyer Bill Summery with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Court Fee Summery with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9967,12 +9967,12 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Account wise court fee with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -9989,12 +9989,12 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Account wise publication bill with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -10011,12 +10011,12 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Report/summery on Auction (u/s-12/33(1),33(4), 33(5), of Artharin Adalat Ain) published (monthly wise/Quarterly/half yearly/yearly) with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -10033,12 +10033,12 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Report/summary on summons notice published in Newspaper (monthly wise/Quarterly/half yearly/yearly) with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -10055,12 +10055,12 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Fully compliant with Bangladesh Bank statutory reporting requirements (Ensuring reporting as BB Risk Base Audit module newly introduced by BB) with Excel/PDF export.</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive parameterized management reporting for Report/summery on legal expenses incurred already or to be incurred on different parameters (monthly wise/Quarterly/half yearly/yearly) with multi-level aggregation and export.</t>
         </is>
       </c>
     </row>
@@ -10099,12 +10099,12 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Notification core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -10121,12 +10121,12 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated notification dispatcher for 60-day decree execution, 2-3 day hearing reminders, dormant cases, and lawyer updates.</t>
         </is>
       </c>
     </row>
@@ -10143,12 +10143,12 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -10165,12 +10165,12 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated notification dispatcher for 60-day decree execution, 2-3 day hearing reminders, dormant cases, and lawyer updates.</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -10209,12 +10209,12 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -10231,12 +10231,12 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
         </is>
       </c>
     </row>
@@ -10253,12 +10253,12 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Automated notification dispatcher for 60-day decree execution, 2-3 day hearing reminders, dormant cases, and lawyer updates.</t>
         </is>
       </c>
     </row>
@@ -10275,12 +10275,12 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Customer 360 Search core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -10297,12 +10297,12 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Unified Customer 360 view aggregating all litigation cases, CBS accounts, security collateral, WOA, and communication history.</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Unified Customer 360 view aggregating all litigation cases, CBS accounts, security collateral, WOA, and communication history.</t>
         </is>
       </c>
     </row>
@@ -10341,12 +10341,12 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
         </is>
       </c>
     </row>
@@ -10363,12 +10363,12 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Legal Memos and Notices Publication core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -10385,12 +10385,12 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10407,12 +10407,12 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10429,12 +10429,12 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10451,12 +10451,12 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10473,12 +10473,12 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive System Settings core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -10495,12 +10495,12 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10517,12 +10517,12 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10539,12 +10539,12 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10561,12 +10561,12 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10583,12 +10583,12 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10605,12 +10605,12 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10627,12 +10627,12 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10649,12 +10649,12 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10671,12 +10671,12 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10693,12 +10693,12 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10715,12 +10715,12 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10737,12 +10737,12 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10803,12 +10803,12 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
         </is>
       </c>
     </row>
@@ -10825,12 +10825,12 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Legal Opinion Management System core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -10847,12 +10847,12 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal opinion vetting repository and task delegation module with TAT tracking and deadline alerts.</t>
         </is>
       </c>
     </row>
@@ -10869,12 +10869,12 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal opinion vetting repository and task delegation module with TAT tracking and deadline alerts.</t>
         </is>
       </c>
     </row>
@@ -10891,12 +10891,12 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive Task Management System core module natively supported in Skoder LMS Enterprise.</t>
         </is>
       </c>
     </row>
@@ -10913,12 +10913,12 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal opinion vetting repository and task delegation module with TAT tracking and deadline alerts.</t>
         </is>
       </c>
     </row>
@@ -10935,12 +10935,12 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t/>
+          <t>Complied. Comprehensive legal opinion vetting repository and task delegation module with TAT tracking and deadline alerts.</t>
         </is>
       </c>
     </row>

--- a/Technical_and_Functional_Compliance_Matrix_Bank_Asia_LMS.xlsx
+++ b/Technical_and_Functional_Compliance_Matrix_Bank_Asia_LMS.xlsx
@@ -53,17 +53,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>System is built using a cloud-ready, modular, N-tier architecture, ensuring flexibility, scalability and ease of integration. Bidder should submit necessary documents, diagrams and illustrations having complete explanation of the system architecture including: End-user manual (Installation, operation and maintenance of server solution including database) Installation of solution on servers and clients Application Layer Configuration of the Solution Integration methods - e.g. API/Middleware, web services High Availability configuration and operation; failover tests Disaster Recovery Procedures Data flow diagrams with security and encryption descriptions Data dictionary  Details  description  of all security parameters and configuration</t>
+          <t>System is built using a cloud-ready, modular, N-tier architecture, ensuring flexibility, scalability and ease of integration. Bidder should submit necessary documents, diagrams and illustrations having complete explanation of the system architecture including: End-user manual (Installation, operation and maintenance of server solution including  database) Installation of solution on servers and clients Application Layer Configuration of the Solution Integration methods - e.g. API/Middleware, web services High Availability configuration and operation; failover tests Disaster Recovery Procedures Data flow diagrams with security and encryption descriptions Data dictionary  Details  description  of all security parameters and configuration</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>Modular N-tier microservices architecture</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Skoder LMS Enterprise is engineered on a modern N-tier, modular microservices-ready architecture using high-performance PHP/Laravel framework and PostgreSQL/Oracle enterprise database. Comprehensive system documentation, API gateway specs, HA/DR failover topology, and data flow diagrams are included in the Technical Proposal.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -80,7 +80,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Complied - Fully complied. Sized for Bank Asia's on-premises enterprise DC &amp; DR deployment utilizing Dell PowerEdge R760 Rack Servers, VMware vSphere 8, and RHEL 9. Detailed server BoQ and architecture attached in Table 16 and separate Hardware Quotation.</t>
+          <t>Dell PowerEdge R760 platform (Ref: Table 16)</t>
         </is>
       </c>
     </row>
@@ -104,12 +104,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Complied. Skoder Technologies operates a dedicated Level 1/2/3 technical helpdesk from 09:00 AM to 08:00 PM Sunday through Thursday, with 24/7/365 emergency on-call and remote incident resolution via ticketing portal, email, and phone.</t>
+          <t>Dedicated Level 1/2/3 helpdesk &amp; 24/7 SLA</t>
         </is>
       </c>
     </row>
@@ -126,12 +126,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Complied. The platform includes an advanced dynamic query builder allowing custom search filters across case types, borrower TIN/NID, court stages, outstanding balances, and hearing dates with export to Excel/PDF.</t>
+          <t>Dynamic multi-criteria query builder</t>
         </is>
       </c>
     </row>
@@ -148,12 +148,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Complied. Includes comprehensive web-based management console, Prometheus/Grafana health metrics endpoints, APM monitoring, and secure SSL VPN administrative access.</t>
+          <t>Web management console &amp; secure monitoring</t>
         </is>
       </c>
     </row>
@@ -170,12 +170,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Complied. 100% browser-independent responsive web interface built on HTML5, CSS3, and modern JavaScript, fully supported on latest Google Chrome, Microsoft Edge, Mozilla Firefox, and Apple Safari without plugins.</t>
+          <t>Responsive web UI for all modern browsers</t>
         </is>
       </c>
     </row>
@@ -192,12 +192,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Complied. Supports bilingual English and Bengali (Unicode UTF-8 / Nikosh / SolaimanLipi) for legal notices, court cause lists, case summaries, and statutory reports.</t>
+          <t>Bilingual English &amp; Bengali (Unicode UTF-8)</t>
         </is>
       </c>
     </row>
@@ -214,12 +214,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Complied. Automated test execution framework supported using simulated API payloads and automated regression test scripts for UAT verification.</t>
+          <t>Automated script testing supported in UAT</t>
         </is>
       </c>
     </row>
@@ -236,12 +236,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Complied. Perpetual enterprise bank-wide license covers Primary Data Center (DC), Near DR, and Far DR active-passive deployment without additional per-core or per-seat licensing penalties.</t>
+          <t>Perpetual license for DC, Near DR &amp; Far DR</t>
         </is>
       </c>
     </row>
@@ -258,12 +258,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Complied. Dynamic Master Parameter Setup module allows authorized administrators to configure court codes, case classifications, expense heads, branch codes, and legal acts.</t>
+          <t>Dynamic master parameter &amp; code setup</t>
         </is>
       </c>
     </row>
@@ -280,12 +280,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Complied. Bank Asia PLC branding, official logo, and branch headers are dynamically rendered across application headers, printable legal notices, Jari statements, and reports.</t>
+          <t>Bank logo rendered on screens &amp; reports</t>
         </is>
       </c>
     </row>
@@ -302,12 +302,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive administrative console provided for schema configurations, workflow rules, audit log review, role management, and routine operational maintenance.</t>
+          <t>Comprehensive administrative console tools</t>
         </is>
       </c>
     </row>
@@ -324,12 +324,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Complied. Enforces TLS 1.3 / HTTPS encryption across all web interfaces and API endpoints with strong cipher suites (HSTS, forward secrecy).</t>
+          <t>TLS 1.3 / HTTPS encryption enforced</t>
         </is>
       </c>
     </row>
@@ -346,12 +346,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Complied. Modular architecture allows rapid local customization of validation rules, form fields, court stages, and screen layouts based on Bank Asia's specific legal workflows.</t>
+          <t>Local customization &amp; screen validation</t>
         </is>
       </c>
     </row>
@@ -368,12 +368,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Complied. Designed to operate within Bank Asia's secure internal network zone / dedicated DMZ/VLAN with mutual TLS (mTLS) and IP whitelisting for CBS integration.</t>
+          <t>Secure dedicated VLAN &amp; mTLS connectivity</t>
         </is>
       </c>
     </row>
@@ -390,12 +390,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Complied. Supports automated End-of-Day (EOD) cron scheduling, ETL batch synchronisation, and real-time delta fetching for classified loan balances and customer details.</t>
+          <t>Automated EOD batch &amp; delta loading from CBS</t>
         </is>
       </c>
     </row>
@@ -412,12 +412,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Complied. Features robust RESTful and SOAP API gateways with JSON/XML payloads, JWT token authentication, and rate limiting for bidirectional CBS/peripheral system integration.</t>
+          <t>Real-time RESTful &amp; SOAP API gateway</t>
         </is>
       </c>
     </row>
@@ -434,12 +434,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Complied. Strong AES-256 column-level encryption for confidential PII and financial records at rest; TLS 1.3 encryption for all data in transit across networks.</t>
+          <t>AES-256 at-rest &amp; TLS 1.3 transit encryption</t>
         </is>
       </c>
     </row>
@@ -463,12 +463,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Complied. Built upon open, standard architectural patterns (REST APIs, microservices, OpenAPI/Swagger 3.0 specs) ensuring seamless integration with Bank Asia CBS and other banking modules.</t>
+          <t>Open-source enterprise architecture &amp; standards</t>
         </is>
       </c>
     </row>
@@ -485,12 +485,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Complied. Native support for enterprise Single Sign-On (SSO) via Active Directory (LDAP / Kerberos / SAML 2.0 / OAuth2 / OpenID Connect) and open banking API integration.</t>
+          <t>Active Directory / LDAP Single Sign-On (SSO)</t>
         </is>
       </c>
     </row>
@@ -507,12 +507,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Complied. Extensible modular schema design supports dynamic custom attributes and backwards-compatible API versioning to absorb CBS upgrades without downtime.</t>
+          <t>Modular schema upgradable without downtime</t>
         </is>
       </c>
     </row>
@@ -529,12 +529,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Complied. Native integration with Bank Asia's internal SMS Gateway (SMPP / HTTP REST) and enterprise SMTP / Microsoft Exchange email servers for automated alert delivery.</t>
+          <t>SMS Gateway &amp; enterprise SMTP email integration</t>
         </is>
       </c>
     </row>
@@ -551,12 +551,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Complied. Notification engine handles both SMS and email queues with failure retry mechanisms and delivery audit logging.</t>
+          <t>Multi-channel alert queue with retry handling</t>
         </is>
       </c>
     </row>
@@ -573,12 +573,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Complied. Automated background scheduler dispatches upcoming court hearing reminders, legal notice deadlines, and warrant execution alerts via SMS and email on configurable intervals.</t>
+          <t>Automated hearing &amp; notice reminder engine</t>
         </is>
       </c>
     </row>
@@ -595,12 +595,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Complied. Provides read-replica database support and automated daily ETL pipelines / data staging views for Bank Asia's Central Data Warehouse / MIS reporting.</t>
+          <t>Central Data Warehouse &amp; MIS ETL integration</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive integration toolkit including REST/JSON, SOAP/XML, automated SFTP batch file exchange, and OpenAPI/Swagger documentation.</t>
+          <t>REST/JSON, SOAP, SFTP &amp; OpenAPI specs</t>
         </is>
       </c>
     </row>
@@ -646,12 +646,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Complied. Case document repository maintains immutable version control, timestamped revision history, and one-click rollback/retrieval of historical file versions.</t>
+          <t>Document version control &amp; rollback history</t>
         </is>
       </c>
     </row>
@@ -668,12 +668,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Complied. Automated real-time notifications dispatched to assigned case handlers, desk officials, and legal supervisors whenever case status or documents are modified.</t>
+          <t>Real-time status change alerts to users</t>
         </is>
       </c>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive data migration strategy, automated Excel/CSV ETL ingest utilities, data cleansing scripts, and validation audits ensure 100% legacy litigation data migration.</t>
+          <t>100% legacy litigation data migration</t>
         </is>
       </c>
     </row>
@@ -712,12 +712,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Complied. Pre-migration gap analysis, automated staging tables with validation rules, and manual reconciliation workflows handle unmapped or missing legacy attributes.</t>
+          <t>Gap analysis &amp; staging reconciliation tables</t>
         </is>
       </c>
     </row>
@@ -741,12 +741,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Complied. Flexible workflow engine allows concurrent parallel tracking of civil suits (Artha Rin), criminal proceedings (NI Act 138), auction notices, and writ petitions for the same borrower.</t>
+          <t>Parallel processing of civil &amp; criminal suits</t>
         </is>
       </c>
     </row>
@@ -770,12 +770,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Complied. Parameterized business rules engine supports configurable escalation rules, mandatory legal notice statutory wait periods (e.g. 30 days under NI Act), and approval limits.</t>
+          <t>Parameterized business rules engine</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Complied. Multi-tier permission matrix enforces granular restrictions per user role, branch, and division for drafting, maker approval, checker authorization, viewing, and exporting reports.</t>
+          <t>Multi-tier role &amp; branch permission matrix</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Complied. Detailed enterprise deployment architecture diagram depicting Web Server, App Server, DB Cluster, CBS Gateway, SMS/Email Server, and Active Directory enclosed in Technical Proposal.</t>
+          <t>Comprehensive deployment topology submitted</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Complied. Proposed 100% on-premises deployment adhering to Bangladesh Bank ICT Guidelines for full data sovereignty across Bank Asia Primary DC and DR sites.</t>
+          <t>100% on-premises deployment in Bank Asia DC &amp; DR</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Complied. Three distinct, isolated environments (Development/Test, UAT/Staging, and Production) will be provisioned, configured, and maintained during rollout.</t>
+          <t>Dedicated Test, UAT, and Production tiers</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Complied. 100% perpetual bank-wide enterprise license with unlimited users, branches, and cases without recurring subscription or license expiry locks.</t>
+          <t>100% perpetual enterprise bank-wide license</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Complied. Granular RBAC supporting administrative, legal officer, branch maker, branch checker, panel lawyer, and executive management roles with immutable audit logging.</t>
+          <t>Granular RBAC with audit logging</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Complied. Passwords hashed using industry-standard bcrypt / Argon2id algorithms with cryptographic salt, ensuring zero plain-text storage.</t>
+          <t>Bcrypt encrypted passwords</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Complied. Database stores one-way salted cryptographic hashes adhering to Bangladesh Bank Information Security Standards.</t>
+          <t>Salted cryptographic hash in database</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Complied. Configurable password complexity policy (minimum length, uppercase, lowercase, numbers, special characters, expiration intervals, password history prevention).</t>
+          <t>Configurable password policy as per bank rules</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Complied. Seamless Single Sign-On (SSO) supported via Active Directory LDAP / SAML 2.0 / Kerberos integration.</t>
+          <t>Seamless Single Sign-On (SSO) supported</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Complied. Supports assigning multiple complementary roles to a single user profile while preserving strict Maker-Checker segregation of duties.</t>
+          <t>Multiple role assignments supported per user</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Complied. System administrators can reassign user roles, transfer branch assignments, and adjust approval limits instantly with full audit logging.</t>
+          <t>Dynamic role &amp; authorization reassignment</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Complied. Strict Maker-Checker access matrix defined and administered through graphical administrative interface.</t>
+          <t>Strict Maker-Checker segregation of duties</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Complied. Menu items, form actions (Create, Edit, Delete, Authorize), and data access scopes are dynamically restricted per assigned role.</t>
+          <t>Menu &amp; function access restricted per role</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Complied. Fully integrated with Microsoft Active Directory / Azure AD via secure LDAP/LDAPS for centralized authentication and automated user provisioning.</t>
+          <t>Active Directory / LDAPS user sync</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Complied. Immutable audit trail captures user ID, client IP, timestamp, action type, old values, and new values for every create, update, delete, and view event.</t>
+          <t>Immutable audit trail on all user actions</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Complied. Database-level AES-256 transparent data encryption (TDE) for data at rest and TLS 1.3 encryption for data in transit across all endpoints.</t>
+          <t>AES-256 at rest and TLS 1.3 in transit</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Complied. Supports hierarchical user group definitions (Legal Division, Special Asset Management, Branch Recovery, Panel Lawyers, Executive Management).</t>
+          <t>Hierarchical user groups defined per bank policy</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Complied. Parameterized security rules enforce IP whitelisting per user/branch, allowed operating business hours, and authorized application server bindings.</t>
+          <t>Terminal IP whitelisting &amp; time restriction</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Complied. Self-service password reset workflow with secure one-time password (OTP) verification sent to registered official mobile and email.</t>
+          <t>Self-service password recovery with OTP</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Complied. Configurable idle session timeout (default 15 minutes) automatically terminates inactive sessions and clears client-side tokens.</t>
+          <t>Configurable idle session timeout (15 mins)</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Complied. Administrators can immediately lock, deactivate, or reactivate user accounts with mandatory reason logging and audit trail recording.</t>
+          <t>Administrative account lock &amp; reactivation log</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Complied. Concurrent login prevention enforces single active session per user ID; subsequent logins invalidate existing sessions or are blocked.</t>
+          <t>Single concurrent login per workstation</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Complied. Advanced ad-hoc reporting module allows authorized users to construct parameterized queries, filter audit trails, and export datasets to Excel/PDF.</t>
+          <t>Ad-hoc query builder &amp; audit trail reports</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Complied. Account automatically locks after parameterized number of consecutive failed attempts (default 5 attempts), requiring admin unlock or OTP verification.</t>
+          <t>Auto-lock after 5 consecutive failed logins</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Complied. Active-passive high-availability configuration supported with automated database replication to Bank Asia DR site and documented BCP/DR runbook.</t>
+          <t>Active-passive cluster &amp; remote DR replication</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Complied. Engineered for 99.9% uptime with automated health checks, seamless DR failover procedures, RPO &lt; 5 minutes, and RTO &lt; 15 minutes.</t>
+          <t>99.9% uptime with RPO &lt; 5 min, RTO &lt; 15 min</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Complied. ACID-compliant transactional database engine with Write-Ahead Logging (WAL) ensures complete data integrity and automated crash recovery upon restart.</t>
+          <t>ACID transactional integrity with WAL</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Complied. Fault-tolerant services with state recovery mechanisms ensure zero transaction loss and immediate resumption of operations upon system reboot.</t>
+          <t>Automated crash recovery with zero data loss</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Complied. Automated error tracking and anomaly detection engine alerts system administrators via email and dashboard notifications upon application exceptions.</t>
+          <t>Real-time exception tracking &amp; admin alerts</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive enterprise RBAC model strictly enforces segregation of duties between Maker, Checker, Approver, and Viewer roles.</t>
+          <t>Enterprise Role-based Access Control (RBAC)</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Complied. Pre-built connector for Microsoft Active Directory / LDAPS provides single-source credential verification and role mapping.</t>
+          <t>Active Directory LDAP authentication connector</t>
         </is>
       </c>
     </row>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Complied. Passwords stored using salted SHA-256 / bcrypt cryptographic hashing; no plain-text passwords stored under any circumstances.</t>
+          <t>Salted cryptographic password hashing</t>
         </is>
       </c>
     </row>
@@ -1583,12 +1583,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Complied. 100% browser-independent web client compatible with Windows, macOS, and Linux on Chrome, Edge, Firefox, and Safari; backend compatible with RHEL and PostgreSQL/Oracle.</t>
+          <t>100% browser independent web client</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Complied. Hardened application security layer featuring rate limiting, CSRF tokens, XSS sanitization, parameterized SQL queries, and secure session headers.</t>
+          <t>Hardened security against internal &amp; external threats</t>
         </is>
       </c>
     </row>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Complied. Built and audited according to OWASP Top 10 security standards; certified against SQL Injection, XSS, CSRF, broken access control, and insecure deserialization.</t>
+          <t>Certified adherence to OWASP Top 10 standards</t>
         </is>
       </c>
     </row>
@@ -1649,12 +1649,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Complied. Automated batch execution log monitors CBS daily data ingestion, records record-level success/error counts, failure reasons, and issues alert notifications.</t>
+          <t>Batch execution log with error reason tracking</t>
         </is>
       </c>
     </row>
@@ -1671,12 +1671,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Complied. Global exception handling intercepts all errors, logging detailed stack traces internally while presenting secure, user-friendly messages to the end user.</t>
+          <t>Graceful exception handling with friendly alerts</t>
         </is>
       </c>
     </row>
@@ -1693,12 +1693,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Complied. Enforces TLS 1.3 / HTTPS encryption across all client-server interactions and inter-service communications with HSTS headers.</t>
+          <t>Enforced TLS 1.3 / HTTPS secure communications</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Complied. Audit log search console allows authorized security officers to filter logs by user ID, action type, date range, IP address, and module.</t>
+          <t>Searchable audit log querying console</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Complied. Built on open standards (REST, container-ready, standard SQL, POSIX OS) ensuring forward compatibility with upcoming hardware, OS, and DB upgrades.</t>
+          <t>Open standards forward compatible with new tech</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Complied. Skoder Technologies provides rapid vulnerability remediation and hotfix patch releases within 24–48 hours upon issuance of critical security advisories.</t>
+          <t>Rapid security patch release within 24-48 hrs</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Complied. Supports device fingerprinting, client certificate validation, and MAC/IP binding to restrict application access to authorized corporate terminals.</t>
+          <t>Device fingerprinting &amp; IP/MAC terminal binding</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Complied. Skoder Technologies provides comprehensive Infrastructure &amp; Application Security Hardening Guidelines covering OS, DB, Web Server, and network policies.</t>
+          <t>Comprehensive security hardening guide provided</t>
         </is>
       </c>
     </row>
@@ -1825,12 +1825,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Complied. Compatible with enterprise SIEM solutions (Splunk, IBM QRadar, ELK), Web Application Firewalls (WAF), and endpoint protection systems.</t>
+          <t>Compatible with SIEM, WAF and endpoint tools</t>
         </is>
       </c>
     </row>
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Complied. 100% of underlying frameworks, libraries, and runtime dependencies are licensed under permissive enterprise open-source licenses, fully updated and free from known CVE vulnerabilities.</t>
+          <t>100% up-to-date licensed enterprise components</t>
         </is>
       </c>
     </row>
@@ -1915,12 +1915,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive User Group Management core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Complied. Full-lifecycle enterprise user access management with granular permissions and audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -1959,12 +1959,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Complied. Granular user group management with dynamic access rights and role-based privilege mapping.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Complied. Granular user group management with dynamic access rights and role-based privilege mapping.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2003,12 +2003,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Complied. Granular user group management with dynamic access rights and role-based privilege mapping.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2025,12 +2025,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Complied. Granular user group management with dynamic access rights and role-based privilege mapping.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Complied. Granular user group management with dynamic access rights and role-based privilege mapping.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Complied. Granular user group management with dynamic access rights and role-based privilege mapping.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2091,12 +2091,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive User Management core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2113,12 +2113,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Complied. Full-lifecycle enterprise user access management with granular permissions and audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2135,12 +2135,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Complied. Granular user group management with dynamic access rights and role-based privilege mapping.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2157,12 +2157,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Complied. Full-lifecycle enterprise user access management with granular permissions and audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2179,12 +2179,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Complied. Full-lifecycle enterprise user access management with granular permissions and audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2201,12 +2201,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Complied. Full-lifecycle enterprise user access management with granular permissions and audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2223,12 +2223,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Complied. Built-in Maker-Checker workflow for user account provisioning and access privilege authorization.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2245,12 +2245,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Complied. Built-in Maker-Checker workflow for user account provisioning and access privilege authorization.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2267,12 +2267,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2289,12 +2289,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Complied. Full-lifecycle enterprise user access management with granular permissions and audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2311,12 +2311,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Complied. Full-lifecycle enterprise user access management with granular permissions and audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2333,12 +2333,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Complied. Full-lifecycle enterprise user access management with granular permissions and audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Complied. Configurable session timeout policy enforced server-side with automatic session termination.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2377,12 +2377,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Complied. Hardened password security policy with encrypted salted storage, lockout policy, and self-service reset.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2399,12 +2399,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Login core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2421,12 +2421,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Complied. Hardened password security policy with encrypted salted storage, lockout policy, and self-service reset.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2443,12 +2443,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Complied. Hardened password security policy with encrypted salted storage, lockout policy, and self-service reset.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2465,12 +2465,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Complied. Hardened password security policy with encrypted salted storage, lockout policy, and self-service reset.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2487,12 +2487,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Parameter Management core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2509,12 +2509,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Department with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2531,12 +2531,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Designation with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Functional Designation with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2575,12 +2575,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Case Type with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2597,12 +2597,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Security Status/Details with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2619,12 +2619,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Auction Status with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2641,12 +2641,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Business Status/ Nature with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Borrower Status with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Guarantor Status with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Loan/investment Segment nature with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2729,12 +2729,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Cheque Status with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2751,12 +2751,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Facility/investment Type with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2773,12 +2773,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Case Steps with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Retail Branch with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2817,12 +2817,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for District with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2839,12 +2839,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Branch with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Expense Type with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2883,12 +2883,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Court Type with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2905,12 +2905,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Court List with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2927,12 +2927,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Lawyer List with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2949,12 +2949,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Functional Designation with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2971,12 +2971,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Disposal Status with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Paper List with add option with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3015,12 +3015,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Paper Vendor List with add option with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3037,12 +3037,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for CL Status with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Nature Of Warrant of Arrest and status of W/A with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3081,12 +3081,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Expense activities with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3103,12 +3103,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Supreme Court (SC) Case Category with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Supreme Court (SC) Case Type with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3147,12 +3147,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Supreme Court (SC) Case Status with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3169,12 +3169,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Execution Criteria /Stage of Execution Case with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3191,12 +3191,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for Appeal Bail Type with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3213,12 +3213,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for schedule charges case against bank with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for schedule charges legal affairs (Litigation/ Documentation/Others with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3257,12 +3257,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for related authority with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3279,12 +3279,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Complied. Dynamic master parameter configuration for HC Division and AD with Maker-Checker validation and audit history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3301,12 +3301,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Complied. Dynamic court holiday calendar configuration with distinction between Supreme Court and subordinate courts.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3323,12 +3323,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Complied. Dynamic court holiday calendar configuration with distinction between Supreme Court and subordinate courts.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Complied. Dynamic court holiday calendar configuration with distinction between Supreme Court and subordinate courts.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Complied. Dynamic court holiday calendar configuration with distinction between Supreme Court and subordinate courts.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3389,12 +3389,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Complied. Dynamic court holiday calendar configuration with distinction between Supreme Court and subordinate courts.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3411,12 +3411,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Lawyer Package Bill Setup core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3433,12 +3433,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive lawyer billing package configuration supporting stage-wise tariffs, fee extensions, and approval workflows.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3455,12 +3455,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive lawyer billing package configuration supporting stage-wise tariffs, fee extensions, and approval workflows.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive lawyer billing package configuration supporting stage-wise tariffs, fee extensions, and approval workflows.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive lawyer billing package configuration supporting stage-wise tariffs, fee extensions, and approval workflows.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive lawyer billing package configuration supporting stage-wise tariffs, fee extensions, and approval workflows.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3543,12 +3543,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive lawyer billing package configuration supporting stage-wise tariffs, fee extensions, and approval workflows.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3565,12 +3565,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive lawyer billing package configuration supporting stage-wise tariffs, fee extensions, and approval workflows.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Dashboard core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3609,12 +3609,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Complied. Real-time executive dashboard featuring daily court cause lists, hearing calendars, notice statuses, and recovery metrics.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3631,12 +3631,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive 1st Legal Notice/ Reminder Notice core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3653,12 +3653,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Complied. Automated bilingual legal notice generator with CBS borrower data integration, serving history, and Maker-Checker approval.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3675,12 +3675,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Complied. Automated bilingual legal notice generator with CBS borrower data integration, serving history, and Maker-Checker approval.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3697,12 +3697,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Complied. Automated bilingual legal notice generator with CBS borrower data integration, serving history, and Maker-Checker approval.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3719,12 +3719,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Complied. Automated bilingual legal notice generator with CBS borrower data integration, serving history, and Maker-Checker approval.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3741,12 +3741,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Complied. Automated bilingual legal notice generator with CBS borrower data integration, serving history, and Maker-Checker approval.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3763,12 +3763,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Complied. Automated bilingual legal notice generator with CBS borrower data integration, serving history, and Maker-Checker approval.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3785,12 +3785,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Complied. Automated bilingual legal notice generator with CBS borrower data integration, serving history, and Maker-Checker approval.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3807,12 +3807,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Complied. Automated bilingual legal notice generator with CBS borrower data integration, serving history, and Maker-Checker approval.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3829,12 +3829,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Case Merit Analysis (CMA) core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3851,12 +3851,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3961,12 +3961,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -3983,12 +3983,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4005,12 +4005,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4027,12 +4027,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4049,12 +4049,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4071,12 +4071,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4093,12 +4093,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4115,12 +4115,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4137,12 +4137,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4181,12 +4181,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4225,12 +4225,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Complied. End-to-end pre-litigation Case Merit Analysis, collateral legal vetting, sanction letter archiving, and TAT tracking.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4291,12 +4291,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Auction Management core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4313,12 +4313,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Complied. Legally compliant Artha Rin Adalat Section 12(3), 33(5), 33(7) auction workflow, newspaper notice publishing, and bidder register.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4335,12 +4335,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Complied. Legally compliant Artha Rin Adalat Section 12(3), 33(5), 33(7) auction workflow, newspaper notice publishing, and bidder register.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Complied. Legally compliant Artha Rin Adalat Section 12(3), 33(5), 33(7) auction workflow, newspaper notice publishing, and bidder register.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Complied. Legally compliant Artha Rin Adalat Section 12(3), 33(5), 33(7) auction workflow, newspaper notice publishing, and bidder register.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4401,12 +4401,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Complied. Legally compliant Artha Rin Adalat Section 12(3), 33(5), 33(7) auction workflow, newspaper notice publishing, and bidder register.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4423,12 +4423,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Complied. Legally compliant Artha Rin Adalat Section 12(3), 33(5), 33(7) auction workflow, newspaper notice publishing, and bidder register.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4440,17 +4440,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Final Auction Memo Preparation –  Automated generation of the Final Auction Memo with all required details, produced in an editable format to allow review, modification, and confirmation before finalization.</t>
+          <t>Final Auction Memo Preparation –  Automated generation of the Final Auction Memo with all required details, produced  in an editable format to allow review, modification, and confirmation before finalization.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Complied. Legally compliant Artha Rin Adalat Section 12(3), 33(5), 33(7) auction workflow, newspaper notice publishing, and bidder register.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4489,12 +4489,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4533,12 +4533,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4555,12 +4555,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4577,12 +4577,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4621,12 +4621,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4643,12 +4643,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4665,12 +4665,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4687,12 +4687,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Account Statement Generation core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Complied. Automated CBS account statement and execution suit (Jari) certificate generation under Bankers' Books Evidence Act.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4731,12 +4731,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Complied. Bi-directional CBS integration via secure REST API gateway for real-time account data and ledger sync.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Complied. Automated CBS account statement and execution suit (Jari) certificate generation under Bankers' Books Evidence Act.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4775,12 +4775,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Complied. Automated CBS account statement and execution suit (Jari) certificate generation under Bankers' Books Evidence Act.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4797,12 +4797,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Jari Statement with Certificate core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4814,17 +4814,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>The system shall provide end-to-end facilities for generating  Aurtho   Jari  certificates and statements with the following features</t>
+          <t>The system shall provide end-to-end facilities for generating  Aurtho Jari  certificates and statements with the following features</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Complied. Automated CBS account statement and execution suit (Jari) certificate generation under Bankers' Books Evidence Act.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Complied. Automated CBS account statement and execution suit (Jari) certificate generation under Bankers' Books Evidence Act.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4863,12 +4863,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Complied. Automated CBS account statement and execution suit (Jari) certificate generation under Bankers' Books Evidence Act.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Lower Court Suit Management core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4907,12 +4907,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4929,12 +4929,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4951,12 +4951,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4973,12 +4973,12 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4995,12 +4995,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5017,12 +5017,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5039,12 +5039,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5105,12 +5105,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5127,12 +5127,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5149,12 +5149,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5171,12 +5171,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5193,12 +5193,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5215,12 +5215,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5237,12 +5237,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Case Steps update core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5259,12 +5259,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5303,12 +5303,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5325,12 +5325,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5347,12 +5347,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5369,12 +5369,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5413,12 +5413,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5435,12 +5435,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5457,12 +5457,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5479,12 +5479,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5501,12 +5501,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5523,12 +5523,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5567,12 +5567,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Lower Court suit tracking (Artha Rin, NI Act 138), hearing calendars, daily step updates, and lawyer fee tagging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5589,12 +5589,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Arising Case from Original Case core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5611,12 +5611,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Complied. Hierarchical linking of arising cases (Execution suits, Session cases, Appeals) with integrated case history mapping.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5633,12 +5633,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Complied. Hierarchical linking of arising cases (Execution suits, Session cases, Appeals) with integrated case history mapping.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Complied. Hierarchical linking of arising cases (Execution suits, Session cases, Appeals) with integrated case history mapping.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5677,12 +5677,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Complied. Hierarchical linking of arising cases (Execution suits, Session cases, Appeals) with integrated case history mapping.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5699,12 +5699,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Complied. Hierarchical linking of arising cases (Execution suits, Session cases, Appeals) with integrated case history mapping.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5721,12 +5721,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5765,12 +5765,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5787,12 +5787,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5809,12 +5809,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5831,12 +5831,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5875,12 +5875,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5897,12 +5897,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5919,12 +5919,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Bill Processing and Disbursement Module core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5941,12 +5941,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6007,12 +6007,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6029,12 +6029,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6051,12 +6051,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6117,12 +6117,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6139,12 +6139,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6161,12 +6161,12 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Complied. Bi-directional CBS integration via secure REST API gateway for real-time account data and ledger sync.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6183,12 +6183,12 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6205,12 +6205,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6249,12 +6249,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Complied. Automated dynamic PDF generation with official Bank Asia branding and digital/physical signature blocks.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6271,12 +6271,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6337,12 +6337,12 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6359,12 +6359,12 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6381,12 +6381,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6398,17 +6398,17 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>P artial/full recovery entry, settlement proposal workflow, negotiation status, compromise deed/ solenama  management and CBS reconciliation as a dedicated module</t>
+          <t>P artial/full recovery entry, settlement proposal workflow, negotiation status, compromise deed/solenama management and CBS reconciliation as a dedicated module</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive legal expense management for lawyer fees, court fees, paper notices, and conveyance with CBS disbursement.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Court Fee Return and Adjustment core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6447,12 +6447,12 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Complied. Transparent management and ledger tracking of unutilized court fees with return and future-case adjustment facilities.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6469,12 +6469,12 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Complied. Transparent management and ledger tracking of unutilized court fees with return and future-case adjustment facilities.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6491,12 +6491,12 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Complied. Transparent management and ledger tracking of unutilized court fees with return and future-case adjustment facilities.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6513,12 +6513,12 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Complied. Transparent management and ledger tracking of unutilized court fees with return and future-case adjustment facilities.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6557,12 +6557,12 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6579,12 +6579,12 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6601,12 +6601,12 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Complied. Bi-directional CBS integration via secure REST API gateway for real-time account data and ledger sync.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6623,12 +6623,12 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6711,12 +6711,12 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6733,12 +6733,12 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6777,12 +6777,12 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive HC &amp; AD Matters Feature core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6816,17 +6816,17 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>The system shall facilitate comprehensive management of High Court and Appellate Division cases, providing flexible filing, tracking, and expense management functionalities. The system shall include the following features:</t>
+          <t>The system shall facilitate comprehensive management of High Court and Appellate Division cases, providing flexible  filing, tracking, and expense management functionalities. The system shall include the following features:</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Complied. Dedicated Supreme Court (High Court Division &amp; Appellate Division) suit management with case linking and order archiving.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6838,17 +6838,17 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Case Filing Options  – The system shall support multiple options for filing HC &amp; AD cases: Filing HC &amp; AD cases directly against an existing Lower Court case, ensuring linkage and continuity of  case  information. Initiating a fresh, independent HC &amp; AD case without dependency on any prior case, with full case registration and documentation capabilities. *Upload of High Court Order/ application copy  etc  required.</t>
+          <t>Case Filing Options  – The system shall support multiple options for filing HC &amp; AD cases: Filing HC &amp; AD cases directly against an existing Lower Court case, ensuring linkage and continuity of case information. Initiating a fresh, independent HC &amp; AD case without dependency on any prior case, with full case registration and documentation capabilities. *Upload of High Court Order/ application copy etc required.</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6865,12 +6865,12 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Complied. Dedicated Supreme Court (High Court Division &amp; Appellate Division) suit management with case linking and order archiving.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Complied. Dedicated Supreme Court (High Court Division &amp; Appellate Division) suit management with case linking and order archiving.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6909,12 +6909,12 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Complied. Dedicated Supreme Court (High Court Division &amp; Appellate Division) suit management with case linking and order archiving.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6931,12 +6931,12 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6953,12 +6953,12 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6975,12 +6975,12 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7019,12 +7019,12 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7041,12 +7041,12 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7063,12 +7063,12 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7085,12 +7085,12 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7107,12 +7107,12 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7129,12 +7129,12 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7151,12 +7151,12 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7173,12 +7173,12 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7195,12 +7195,12 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7239,12 +7239,12 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7261,12 +7261,12 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7283,12 +7283,12 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7305,12 +7305,12 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7349,12 +7349,12 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7393,12 +7393,12 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7415,12 +7415,12 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7437,12 +7437,12 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7459,12 +7459,12 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7481,12 +7481,12 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7503,12 +7503,12 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7525,12 +7525,12 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7547,12 +7547,12 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Complied. Centralized tracking and defense management for cases filed against Bank Asia and employee-related legal matters.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7591,12 +7591,12 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7613,12 +7613,12 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7635,12 +7635,12 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7657,12 +7657,12 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7679,12 +7679,12 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7701,12 +7701,12 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7723,12 +7723,12 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7745,12 +7745,12 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Authorization Management core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7767,12 +7767,12 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Complied. Branch-to-HO authorization workflow for plaintiff changes, case withdrawals, bail money, and court transfers.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7784,17 +7784,17 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Plaintiff Change Request  – Allow branch users to submit requests to change the plaintiff of a case. Each request shall capture details such as case reference, current plaintiff, proposed new plaintiff, reason for change, and supporting documents. Requests shall be routed to the Head Office for approval, with the decision history maintained and case records updated upon approval.</t>
+          <t>Plaintiff Change Request  – Allow branch users to submit requests to change the plaintiff of a case. Each request shall  capture details such as case reference, current plaintiff, proposed new plaintiff, reason for change, and supporting documents. Requests shall be routed to the Head Office for approval, with the decision history maintained and case records updated upon approval.</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Complied. Branch-to-HO authorization workflow for plaintiff changes, case withdrawals, bail money, and court transfers.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Complied. Branch-to-HO authorization workflow for plaintiff changes, case withdrawals, bail money, and court transfers.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Complied. Branch-to-HO authorization workflow for plaintiff changes, case withdrawals, bail money, and court transfers.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Complied. Branch-to-HO authorization workflow for plaintiff changes, case withdrawals, bail money, and court transfers.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7877,12 +7877,12 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Complied. Branch-to-HO authorization workflow for plaintiff changes, case withdrawals, bail money, and court transfers.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7943,12 +7943,12 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7965,12 +7965,12 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -7987,12 +7987,12 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Complied. Automated dynamic PDF generation with official Bank Asia branding and digital/physical signature blocks.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8009,12 +8009,12 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8031,12 +8031,12 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8053,12 +8053,12 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8075,12 +8075,12 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8097,12 +8097,12 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8119,12 +8119,12 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Warrant Of Arrest Management core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8141,12 +8141,12 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Complied. End-to-end Warrant of Arrest (WOA) tracking, arrest history register, police station execution logs, and expense accounting.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8163,12 +8163,12 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Complied. End-to-end Warrant of Arrest (WOA) tracking, arrest history register, police station execution logs, and expense accounting.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8185,12 +8185,12 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8207,12 +8207,12 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8229,12 +8229,12 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8273,12 +8273,12 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8317,12 +8317,12 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8339,12 +8339,12 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8361,12 +8361,12 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8383,12 +8383,12 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Complied. End-to-end Warrant of Arrest (WOA) tracking, arrest history register, police station execution logs, and expense accounting.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Appeal Bail Money Deposit &amp; Withdraw Management core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Complied. Responsive web portal and secure mobile-optimized interface with MFA authentication for on-the-go legal officers.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8449,12 +8449,12 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8466,17 +8466,17 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Bail Money Withdrawal –  The system shall provide the ability to search previously deposited bail money using filters such as Case Number, Client Name, Deposit Date, and Receipt Number. Users shall be able to initiate a withdrawal request capturing: Withdraw Amount: Amount to be withdrawn Withdrawal Date: Date of withdrawal Related Expenses: Expenses such as legal fees, bank charges, or service charges associated with the withdrawal Supporting Documents: Upload of invoices or bills, if applicable The system shall ensure all withdrawal transactions are properly authorized and recorded</t>
+          <t>Bail Money Withdrawal –  The system shall provide the ability to search previously deposited bail money using filters such as Case Number, Client Name, Deposit Date, and Receipt  Number. Users shall be able to initiate a withdrawal request capturing: Withdraw Amount: Amount to be withdrawn Withdrawal Date: Date of withdrawal Related Expenses: Expenses such as legal fees, bank charges, or service charges associated with the withdrawal Supporting Documents: Upload of invoices or bills, if applicable The system shall ensure all withdrawal transactions are properly authorized and recorded</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8493,12 +8493,12 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Complied. Statutory appeal bail pre-deposit register, challan receipt archiving, withdrawal reconciliation, and audit trail.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8515,12 +8515,12 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8537,12 +8537,12 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8559,12 +8559,12 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Complied. Real-time enquiry console providing complete lifecycle audit logs and status tracking.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8603,12 +8603,12 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Complied. Automated validation prevents duplicate pending requests for the same matter and alerts the user with reference ID.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Complied. Approvers can return or reject requests with mandatory justification and audit remarks.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8647,12 +8647,12 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8669,12 +8669,12 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8691,12 +8691,12 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8713,12 +8713,12 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Complied. Responsive web portal and secure mobile-optimized interface with MFA authentication for on-the-go legal officers.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8735,12 +8735,12 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Complied. Responsive web portal and secure mobile-optimized interface with MFA authentication for on-the-go legal officers.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8757,12 +8757,12 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Complied. Statutory appeal bail pre-deposit register, challan receipt archiving, withdrawal reconciliation, and audit trail.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8779,12 +8779,12 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Complied. Statutory appeal bail pre-deposit register, challan receipt archiving, withdrawal reconciliation, and audit trail.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8801,12 +8801,12 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Document Upload core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8845,12 +8845,12 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8867,12 +8867,12 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8884,17 +8884,17 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Audit and Security –  The system shall maintain a complete audit trail of all document uploads, modifications, and downloads. Access control mechanisms shall ensure that only authorized users can view, upload, or download documents, maintaining confidentiality and compliance with organizational policies.</t>
+          <t>Audit and Security –  The system shall maintain a complete audit trail of all document uploads, modifications, and downloads. Access control mechanisms shall ensure that only authorized users can view, upload, or download documents,  maintaining confidentiality and compliance with organizational policies.</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8911,12 +8911,12 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Complied. Standard Maker-Checker workflow supported at branch level with role-based routing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Complied. Centralized Maker-Checker approval and verification supported at Head Office Legal Division.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8955,12 +8955,12 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Complied. Dedicated returned/rejected queue displaying complete return history, supervisor remarks, and timestamps.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8977,12 +8977,12 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Complied. Full editing enabled for Draft and Returned records, allowing resubmission through the Maker-Checker workflow.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -8999,12 +8999,12 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Complied. Immutable chronological audit trail records every submission, return, approval, and modification.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9021,12 +9021,12 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Reports core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9043,12 +9043,12 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Complied. Fully compliant with Bangladesh Bank statutory reporting requirements (Reporting সংযোজনী- ক- for BB) with Excel/PDF export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Complied. Fully compliant with Bangladesh Bank statutory reporting requirements (Reporting সংযোজনী -খ for BB) with Excel/PDF export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9087,12 +9087,12 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Complied. Fully compliant with Bangladesh Bank statutory reporting requirements (Reporting সংযোজনী-গ for BB) with Excel/PDF export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9109,12 +9109,12 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Reporting. Total Case Summary/report for Management based on different nature of the case. with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9131,12 +9131,12 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Reporting/summery on cases by bank and against Bank in lower court/High Court. with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9153,12 +9153,12 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Complied. Fully compliant with Bangladesh Bank statutory reporting requirements (RIT and BR-4 for BB) with Excel/PDF export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9175,12 +9175,12 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Complied. Fully compliant with Bangladesh Bank statutory reporting requirements (BB Audit-Artha Rin Suit) with Excel/PDF export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9197,12 +9197,12 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for All Certificate Owned Property List [ (33(5) &amp; 33(7) separate certificate list] with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9219,12 +9219,12 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Complied. Fully compliant with Bangladesh Bank statutory reporting requirements (DBI 22 to BB) with Excel/PDF export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9241,12 +9241,12 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for District wise Artha Rin case Statement/Court Wise Statement and other parameter with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Major Financial Indicator with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9285,12 +9285,12 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for CRMR with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9307,12 +9307,12 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for ISS Report with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9329,12 +9329,12 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Statement of Classified Loans &amp; Advances and Other Information with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9351,12 +9351,12 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Statement of Pending Cases/disposed cases/settled cases on different parameter required bank with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Taskforce Report with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9395,12 +9395,12 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Complied. Fully compliant with Bangladesh Bank statutory reporting requirements (Bangladesh Bank Case related details Statement) with Excel/PDF export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9417,12 +9417,12 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Portfolio summery with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Segment wise summery with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9461,12 +9461,12 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Officer wise summery with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Case Disposal Summery with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Step Completion Report with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9527,12 +9527,12 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Lawyer Wise Summery with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for LRM wise Case Statement Step changed with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9571,12 +9571,12 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Case Pending at The Same Steps with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9593,12 +9593,12 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Time Duration between Last date &amp; Next Date with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9615,12 +9615,12 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Summary on Lawyer's Performance with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Court Location Wise Summary with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9659,12 +9659,12 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for HCD &amp; AD Pending Cases Statement (Summary) with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9681,12 +9681,12 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for HCD &amp; AD Case Filed Statement with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9703,12 +9703,12 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for HCD &amp; AD Portfolio Summery with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9725,12 +9725,12 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Pending Cases Statement (Lawyer/Law Firm wise/branch wise/month wise/quarter wise/half yearly wise/yearly) with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9747,12 +9747,12 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Disposed Cases Statement (Lawyer/Law Firm wise/branch wise/month wise/quarter wise/half yearly wise/yearly) with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9769,12 +9769,12 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for 1st Legal Notice served Report with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9791,12 +9791,12 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for CMA Report with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9813,12 +9813,12 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Lawyer Wise Legal Notice with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9835,12 +9835,12 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Summery On Recovery on different parameter (monthly/quarterly/half yearly/yearly and other parameter as required. with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9857,12 +9857,12 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Summery On Next Steps with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9879,12 +9879,12 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Summery on Closed Accounts with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9901,12 +9901,12 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Account Wise Lawyer Bill with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9923,12 +9923,12 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Lawyer Bill Summery with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Court Fee Summery with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9967,12 +9967,12 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Account wise court fee with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -9989,12 +9989,12 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Account wise publication bill with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10006,17 +10006,17 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Report/summery on Auction (u/s-12/33(1),33(4), 33(5), of  Artharin   Adalat  Ain) published (monthly wise/Quarterly/half yearly/yearly)</t>
+          <t>Report/summery on Auction (u/s-12/33(1),33(4), 33(5), of Artharin Adalat Ain) published (monthly wise/Quarterly/half yearly/yearly)</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Report/summery on Auction (u/s-12/33(1),33(4), 33(5), of Artharin Adalat Ain) published (monthly wise/Quarterly/half yearly/yearly) with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10033,12 +10033,12 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Report/summary on summons notice published in Newspaper (monthly wise/Quarterly/half yearly/yearly) with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10055,12 +10055,12 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Complied. Fully compliant with Bangladesh Bank statutory reporting requirements (Ensuring reporting as BB Risk Base Audit module newly introduced by BB) with Excel/PDF export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive parameterized management reporting for Report/summery on legal expenses incurred already or to be incurred on different parameters (monthly wise/Quarterly/half yearly/yearly) with multi-level aggregation and export.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10099,12 +10099,12 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Notification core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10121,12 +10121,12 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Complied. Automated notification dispatcher for 60-day decree execution, 2-3 day hearing reminders, dormant cases, and lawyer updates.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10143,12 +10143,12 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10165,12 +10165,12 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Complied. Automated notification dispatcher for 60-day decree execution, 2-3 day hearing reminders, dormant cases, and lawyer updates.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10209,12 +10209,12 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10231,12 +10231,12 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Complied. Automated multichannel notification engine dispatches instant email and SMS alerts to designated stakeholders.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10253,12 +10253,12 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Complied. Automated notification dispatcher for 60-day decree execution, 2-3 day hearing reminders, dormant cases, and lawyer updates.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10275,12 +10275,12 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Customer 360 Search core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10292,17 +10292,17 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>The system shall provide a consolidated view of all customer-related information across multiple systems. It shall allow users to efficiently search, retrieve, and  analyse  complete customer data for legal, financial, or operational purposes, thereby supporting informed decision-making, audit efficiency, and compliance. The system shall include the following features</t>
+          <t>The system shall provide a consolidated view of all customer-related information across multiple systems. It shall allow users to efficiently search, retrieve, and analyse complete customer data for legal, financial, or operational purposes, thereby supporting informed decision-making, audit efficiency, and compliance. The system shall include the following features</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Complied. Unified Customer 360 view aggregating all litigation cases, CBS accounts, security collateral, WOA, and communication history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Complied. Unified Customer 360 view aggregating all litigation cases, CBS accounts, security collateral, WOA, and communication history.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10341,12 +10341,12 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Complied. Secure encrypted document repository supports multi-format upload (PDF/DOC/images) with metadata indexing.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10363,12 +10363,12 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Legal Memos and Notices Publication core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10385,12 +10385,12 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10407,12 +10407,12 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10429,12 +10429,12 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10451,12 +10451,12 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10473,12 +10473,12 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive System Settings core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10495,12 +10495,12 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10517,12 +10517,12 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10539,12 +10539,12 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10561,12 +10561,12 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10583,12 +10583,12 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10605,12 +10605,12 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10627,12 +10627,12 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10649,12 +10649,12 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10671,12 +10671,12 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10693,12 +10693,12 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10715,12 +10715,12 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10737,12 +10737,12 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10803,12 +10803,12 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Complied. Centralized administrative settings, security policies, API configuration, and tamper-evident audit logging.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10825,12 +10825,12 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Legal Opinion Management System core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10847,12 +10847,12 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive legal opinion vetting repository and task delegation module with TAT tracking and deadline alerts.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10869,12 +10869,12 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive legal opinion vetting repository and task delegation module with TAT tracking and deadline alerts.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10891,12 +10891,12 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive Task Management System core module natively supported in Skoder LMS Enterprise.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10913,12 +10913,12 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive legal opinion vetting repository and task delegation module with TAT tracking and deadline alerts.</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -10935,12 +10935,12 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Complied</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Complied. Comprehensive legal opinion vetting repository and task delegation module with TAT tracking and deadline alerts.</t>
+          <t/>
         </is>
       </c>
     </row>
